--- a/examples/audit_workbook.xlsx
+++ b/examples/audit_workbook.xlsx
@@ -85,7 +85,7 @@
     <t>Executive summary</t>
   </si>
   <si>
-    <t>Housing Stability Grant</t>
+    <t>Stable Homes Grant</t>
   </si>
   <si>
     <t>housing_stability</t>
@@ -94,7 +94,7 @@
     <t>B</t>
   </si>
   <si>
-    <t>Audited 263 records for Housing Stability Grant: overall data quality score 85.1/100 (grade B). Findings by severity: 9 critical, 31 high, 27 medium, 10 low, 38 informational. 5 blocking issue type(s) must be resolved before submission: Missing required fields, Missing exit destination, Duplicate client enrollment, Unknown program. Largest issues: Duplicate client enrollment (6 records); Exit before enrollment (3 records); Missing required fields (4 records).</t>
+    <t>Audited 263 records for Stable Homes Grant: overall data quality score 85.1/100 (grade B). Findings by severity: 9 critical, 31 high, 27 medium, 10 low, 38 informational. 5 blocking issue type(s) must be resolved before submission: Missing required fields, Missing exit destination, Exit before enrollment, Duplicate client enrollment. Largest issues: Duplicate client enrollment (6 records); Exit before enrollment (3 records); Missing required fields (4 records).</t>
   </si>
   <si>
     <t>Item</t>
@@ -124,10 +124,13 @@
     <t>DQ-004</t>
   </si>
   <si>
+    <t>DQ-033</t>
+  </si>
+  <si>
     <t>DQ-024</t>
   </si>
   <si>
-    <t>DQ-033</t>
+    <t>DQ-031</t>
   </si>
   <si>
     <t>DQ-020</t>
@@ -136,9 +139,6 @@
     <t>DQ-026</t>
   </si>
   <si>
-    <t>DQ-031</t>
-  </si>
-  <si>
     <t>DQ-032</t>
   </si>
   <si>
@@ -148,15 +148,15 @@
     <t>DQ-028</t>
   </si>
   <si>
+    <t>DQ-040</t>
+  </si>
+  <si>
+    <t>DQ-041</t>
+  </si>
+  <si>
     <t>DQ-023</t>
   </si>
   <si>
-    <t>DQ-040</t>
-  </si>
-  <si>
-    <t>DQ-041</t>
-  </si>
-  <si>
     <t>DQ-022</t>
   </si>
   <si>
@@ -196,10 +196,13 @@
     <t>Missing exit destination</t>
   </si>
   <si>
+    <t>Status contradicts exit date</t>
+  </si>
+  <si>
     <t>Negative income</t>
   </si>
   <si>
-    <t>Status contradicts exit date</t>
+    <t>Follow-up before exit</t>
   </si>
   <si>
     <t>Invalid date value</t>
@@ -208,9 +211,6 @@
     <t>Unknown program</t>
   </si>
   <si>
-    <t>Follow-up before exit</t>
-  </si>
-  <si>
     <t>Household composition mismatch</t>
   </si>
   <si>
@@ -220,15 +220,15 @@
     <t>Unexpected value in controlled field</t>
   </si>
   <si>
+    <t>Missing required assessment</t>
+  </si>
+  <si>
+    <t>Missing exit plan</t>
+  </si>
+  <si>
     <t>Invalid household counts</t>
   </si>
   <si>
-    <t>Missing required assessment</t>
-  </si>
-  <si>
-    <t>Missing exit plan</t>
-  </si>
-  <si>
     <t>Invalid age</t>
   </si>
   <si>
@@ -310,10 +310,13 @@
     <t>Exited clients have no destination recorded. Housing outcome measures (including permanent housing rate) exclude these exits.</t>
   </si>
   <si>
+    <t>Records are marked Active but have an exit date, or marked Exited with no exit date. Active/exit counts depend on which field you trust.</t>
+  </si>
+  <si>
     <t>Income cannot be negative. Negative values corrupt average and median income calculations and income-change measures.</t>
   </si>
   <si>
-    <t>Records are marked Active but have an exit date, or marked Exited with no exit date. Active/exit counts depend on which field you trust.</t>
+    <t>Post-exit follow-up dates fall before the client's exit date, so they cannot be valid follow-up contacts.</t>
   </si>
   <si>
     <t>Date fields contain values that are not valid dates (for example text or impossible calendar dates). These records are excluded from date-based metrics.</t>
@@ -322,9 +325,6 @@
     <t>Program labels do not match any program or alias defined in the grant profile. These records cannot be attributed to a funded program.</t>
   </si>
   <si>
-    <t>Post-exit follow-up dates fall before the client's exit date, so they cannot be valid follow-up contacts.</t>
-  </si>
-  <si>
     <t>Adults plus children does not add up to the recorded household size, so adult/child population counts and household metrics disagree with each other.</t>
   </si>
   <si>
@@ -334,15 +334,15 @@
     <t>Fields with controlled vocabularies (statuses, destinations, demographic codes) contain values outside the allowed list, so they cannot be categorized correctly.</t>
   </si>
   <si>
+    <t>Clients do not have a completed required assessment on file.</t>
+  </si>
+  <si>
+    <t>Clients exited the program without a completed exit plan, which many funders require for every exit.</t>
+  </si>
+  <si>
     <t>Household size must be between 1 and 12, and adult/child counts cannot be negative. These values distort household and population counts.</t>
   </si>
   <si>
-    <t>Clients do not have a completed required assessment on file.</t>
-  </si>
-  <si>
-    <t>Clients exited the program without a completed exit plan, which many funders require for every exit.</t>
-  </si>
-  <si>
     <t>Ages are negative or above 110, which indicates data entry errors. Age-group breakdowns will misclassify these clients.</t>
   </si>
   <si>
@@ -382,10 +382,13 @@
     <t>Determine the destination from exit paperwork and record it before reporting.</t>
   </si>
   <si>
+    <t>Reconcile the enrollment status with the exit date for each flagged record.</t>
+  </si>
+  <si>
     <t>Correct the sign or re-enter the amount; use 0 for no income.</t>
   </si>
   <si>
-    <t>Reconcile the enrollment status with the exit date for each flagged record.</t>
+    <t>Verify the follow-up date; if the contact happened pre-exit it does not count as a post-exit follow-up.</t>
   </si>
   <si>
     <t>Correct the values to real dates in a consistent format (YYYY-MM-DD recommended).</t>
@@ -394,9 +397,6 @@
     <t>Fix the program name in the data, or add the label as an alias in the profile if it is legitimate.</t>
   </si>
   <si>
-    <t>Verify the follow-up date; if the contact happened pre-exit it does not count as a post-exit follow-up.</t>
-  </si>
-  <si>
     <t>Recount household members and align the three fields.</t>
   </si>
   <si>
@@ -406,13 +406,13 @@
     <t>Map each unexpected value to an allowed option, or update the profile's controlled_values if the option is legitimate.</t>
   </si>
   <si>
+    <t>Schedule and complete the assessment; record its status in the source system.</t>
+  </si>
+  <si>
+    <t>Complete and file exit plans for the flagged clients where possible; review exit procedures with case managers.</t>
+  </si>
+  <si>
     <t>Correct the household composition from intake records.</t>
-  </si>
-  <si>
-    <t>Schedule and complete the assessment; record its status in the source system.</t>
-  </si>
-  <si>
-    <t>Complete and file exit plans for the flagged clients where possible; review exit procedures with case managers.</t>
   </si>
   <si>
     <t>Verify each client's date of birth and correct the age.</t>
@@ -3180,7 +3180,7 @@
         <v>59</v>
       </c>
       <c r="C9" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D9" t="s">
         <v>84</v>
@@ -3206,7 +3206,7 @@
         <v>60</v>
       </c>
       <c r="C10" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D10" t="s">
         <v>84</v>
@@ -3232,7 +3232,7 @@
         <v>61</v>
       </c>
       <c r="C11" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D11" t="s">
         <v>84</v>
@@ -3264,7 +3264,7 @@
         <v>84</v>
       </c>
       <c r="E12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F12">
         <v>2</v>
@@ -3284,13 +3284,13 @@
         <v>63</v>
       </c>
       <c r="C13" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D13" t="s">
         <v>84</v>
       </c>
       <c r="E13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F13">
         <v>2</v>
@@ -3388,7 +3388,7 @@
         <v>67</v>
       </c>
       <c r="C17" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D17" t="s">
         <v>85</v>
@@ -3440,7 +3440,7 @@
         <v>69</v>
       </c>
       <c r="C19" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D19" t="s">
         <v>85</v>
@@ -4308,10 +4308,10 @@
     </row>
     <row r="19" spans="1:12">
       <c r="A19" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B19" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C19" t="s">
         <v>77</v>
@@ -4338,18 +4338,18 @@
         <v>265</v>
       </c>
       <c r="K19" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L19" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="20" spans="1:12">
       <c r="A20" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B20" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C20" t="s">
         <v>81</v>
@@ -4376,10 +4376,10 @@
         <v>266</v>
       </c>
       <c r="K20" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="L20" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -4422,10 +4422,10 @@
     </row>
     <row r="22" spans="1:12">
       <c r="A22" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B22" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C22" t="s">
         <v>81</v>
@@ -4452,10 +4452,10 @@
         <v>266</v>
       </c>
       <c r="K22" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L22" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -4533,10 +4533,10 @@
     </row>
     <row r="25" spans="1:12">
       <c r="A25" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B25" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C25" t="s">
         <v>77</v>
@@ -4563,10 +4563,10 @@
         <v>267</v>
       </c>
       <c r="K25" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="L25" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="26" spans="1:12">
@@ -4609,10 +4609,10 @@
     </row>
     <row r="27" spans="1:12">
       <c r="A27" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B27" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C27" t="s">
         <v>77</v>
@@ -4639,10 +4639,10 @@
         <v>268</v>
       </c>
       <c r="K27" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="L27" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="28" spans="1:12">
@@ -4799,10 +4799,10 @@
     </row>
     <row r="32" spans="1:12">
       <c r="A32" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B32" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C32" t="s">
         <v>81</v>
@@ -4829,10 +4829,10 @@
         <v>266</v>
       </c>
       <c r="K32" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L32" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="33" spans="1:12">
@@ -5255,10 +5255,10 @@
     </row>
     <row r="44" spans="1:12">
       <c r="A44" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C44" t="s">
         <v>81</v>
@@ -5285,10 +5285,10 @@
         <v>266</v>
       </c>
       <c r="K44" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L44" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="45" spans="1:12">
@@ -5407,10 +5407,10 @@
     </row>
     <row r="48" spans="1:12">
       <c r="A48" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B48" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C48" t="s">
         <v>81</v>
@@ -5437,10 +5437,10 @@
         <v>266</v>
       </c>
       <c r="K48" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="L48" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="49" spans="1:12">
@@ -5591,10 +5591,10 @@
     </row>
     <row r="53" spans="1:12">
       <c r="A53" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B53" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C53" t="s">
         <v>80</v>
@@ -5621,10 +5621,10 @@
         <v>279</v>
       </c>
       <c r="K53" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L53" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="54" spans="1:12">
@@ -5705,10 +5705,10 @@
     </row>
     <row r="56" spans="1:12">
       <c r="A56" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B56" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C56" t="s">
         <v>80</v>
@@ -5735,10 +5735,10 @@
         <v>281</v>
       </c>
       <c r="K56" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L56" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="57" spans="1:12">
@@ -5895,10 +5895,10 @@
     </row>
     <row r="61" spans="1:12">
       <c r="A61" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B61" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C61" t="s">
         <v>80</v>
@@ -5925,10 +5925,10 @@
         <v>237</v>
       </c>
       <c r="K61" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L61" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="62" spans="1:12">
@@ -6155,10 +6155,10 @@
     </row>
     <row r="68" spans="1:12">
       <c r="A68" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B68" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C68" t="s">
         <v>80</v>
@@ -6185,10 +6185,10 @@
         <v>284</v>
       </c>
       <c r="K68" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L68" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="69" spans="1:12">
@@ -6269,10 +6269,10 @@
     </row>
     <row r="71" spans="1:12">
       <c r="A71" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B71" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C71" t="s">
         <v>80</v>
@@ -6299,10 +6299,10 @@
         <v>285</v>
       </c>
       <c r="K71" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L71" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="72" spans="1:12">
@@ -6342,10 +6342,10 @@
     </row>
     <row r="73" spans="1:12">
       <c r="A73" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B73" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C73" t="s">
         <v>77</v>
@@ -6372,10 +6372,10 @@
         <v>265</v>
       </c>
       <c r="K73" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L73" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="74" spans="1:12">
@@ -6602,10 +6602,10 @@
     </row>
     <row r="80" spans="1:12">
       <c r="A80" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B80" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C80" t="s">
         <v>81</v>
@@ -6632,10 +6632,10 @@
         <v>266</v>
       </c>
       <c r="K80" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="L80" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="81" spans="1:12">
@@ -6970,10 +6970,10 @@
     </row>
     <row r="90" spans="1:12">
       <c r="A90" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B90" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C90" t="s">
         <v>80</v>
@@ -7000,18 +7000,18 @@
         <v>293</v>
       </c>
       <c r="K90" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L90" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="91" spans="1:12">
       <c r="A91" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B91" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C91" t="s">
         <v>77</v>
@@ -7038,10 +7038,10 @@
         <v>294</v>
       </c>
       <c r="K91" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L91" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="92" spans="1:12">
@@ -7084,10 +7084,10 @@
     </row>
     <row r="93" spans="1:12">
       <c r="A93" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B93" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C93" t="s">
         <v>80</v>
@@ -7114,18 +7114,18 @@
         <v>284</v>
       </c>
       <c r="K93" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L93" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="94" spans="1:12">
       <c r="A94" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B94" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C94" t="s">
         <v>80</v>
@@ -7152,10 +7152,10 @@
         <v>284</v>
       </c>
       <c r="K94" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L94" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="95" spans="1:12">
@@ -7598,10 +7598,10 @@
     </row>
     <row r="107" spans="1:12">
       <c r="A107" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B107" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C107" t="s">
         <v>80</v>
@@ -7628,10 +7628,10 @@
         <v>279</v>
       </c>
       <c r="K107" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L107" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="108" spans="1:12">
@@ -7674,10 +7674,10 @@
     </row>
     <row r="109" spans="1:12">
       <c r="A109" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B109" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C109" t="s">
         <v>80</v>
@@ -7704,10 +7704,10 @@
         <v>237</v>
       </c>
       <c r="K109" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L109" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="110" spans="1:12">
